--- a/J30/Output_files/iLPN_search_results.xlsx
+++ b/J30/Output_files/iLPN_search_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,12 +505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1104QA1040</t>
+          <t>VGASN1107QA2830</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V11042025QA1783600</t>
+          <t>00V11072025QA6969400</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>STORAGE</t>
+          <t>IN_VAS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PO11047937</t>
+          <t>PO11072953</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -565,21 +565,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1104QA1040</t>
+          <t>VGASN1107QA2830</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V11042025QA6105801</t>
+          <t>00V11072025QA8085801</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>136027-115-9.5</t>
@@ -595,10 +603,550 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>PO11047937</t>
+          <t>PO11072953</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00V11072025QA6618802</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>PO11072953</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00V11072025QA3998003</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>PO11072953</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00V11072025QA5036804</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>MEASUREMENT</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>PO11072953</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00V11072025QA7690607</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MIXED_SKU</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>PO11073388</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00V11072025QA1452008</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MIXED_SKU</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>PO11073388</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00V11072025QA1481505</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FIRST_SKU</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>PO11075725</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00V11072025QA7682306</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>PO11075725</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00V11072025QA7690607</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MIXED_SKU</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>PO11073388</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00V11072025QA1452008</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MIXED_SKU</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>PO11073388</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
@@ -615,7 +1163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -718,27 +1266,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1104QA1040</t>
+          <t>VGASN1107QA2830</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V11042025QA1783600</t>
+          <t>00V11072025QA6969400</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>900000880</t>
+          <t>900000952</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -757,16 +1309,512 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PO11047937</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>3301002201</t>
-        </is>
-      </c>
+          <t>PO11072953</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1904000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00V11072025QA8085801</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>900000952</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>PO11072953</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00V11072025QA6618802</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>900000952</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>PO11072953</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00V11072025QA3998003</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>900000952</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>PO11072953</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00V11072025QA5036804</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>900000952</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>PO11072953</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00V11072025QA1481505</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>900000952</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>PO11075725</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00V11072025QA7682306</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>900000952</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>PO11075725</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00V11072025QA7690607</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>900000952</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>PO11073388</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00V11072025QA1452008</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>900000952</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>PO11073388</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -779,9 +1827,1055 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ENVN</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ASN_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>iLPN_ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ItemID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source_LPN</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Condition_Code_type</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Condition_Code_Desc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>UserId</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>00V11072025QA6969400</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>FL - In-VAS Full inspection</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00V11072025QA5036804</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ME - Measurement</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00V11072025QA3998003</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>OT - In-VAS other</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00V11072025QA6618802</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PW - In-VAS PI work</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00V11072025QA6969400</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>QA - Quality Audit/Fail</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00V11072025QA5036804</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00V11072025QA7682306</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FL - In-VAS Full inspection</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00V11072025QA1481505</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>FS - 1st SKU</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00V11072025QA7682306</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>OT - In-VAS other</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00V11072025QA7682306</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PW - In-VAS PI work</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00V11072025QA7682306</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00V11072025QA1481505</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00V11072025QA7690607</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MS - Multi-SKU</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00V11072025QA7690607</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MS - Multi-SKU</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00V11072025QA1452008</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MS - Multi-SKU</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00V11072025QA1452008</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MS - Multi-SKU</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00V11072025QA1452008</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00V11072025QA1452008</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00V11072025QA7690607</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00V11072025QA7690607</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/J30/Output_files/iLPN_search_results.xlsx
+++ b/J30/Output_files/iLPN_search_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,12 +505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1113QA3680</t>
+          <t>VGASN1125QA4410</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V11132025QA8179602</t>
+          <t>00V11252025QA8409300</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>STORAGE</t>
+          <t>MIXED_SKU</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CJ2242-100-L</t>
+          <t>420420-420-M</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PO11133893</t>
+          <t>PO11255748</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1113QA3680</t>
+          <t>VGASN1125QA4410</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V11132025QA4986703</t>
+          <t>00V11252025QA9579401</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>STORAGE</t>
+          <t>MIXED_SKU</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CJ2242-100-M</t>
+          <t>420420-420-M</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -603,7 +603,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>PO11138664</t>
+          <t>PO11255748</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,12 +625,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VGASN1113QA3680</t>
+          <t>VGASN1125QA4410</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00V11132025QA9951904</t>
+          <t>00V11252025QA8409300</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>STORAGE</t>
+          <t>MIXED_SKU</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DC4244-291-MISC</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>PO11132929</t>
+          <t>PO11255748</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VGASN1113QA3680</t>
+          <t>VGASN1125QA4410</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00V11132025QA3861905</t>
+          <t>00V11252025QA9579401</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>STORAGE</t>
+          <t>MIXED_SKU</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DC4244-328-MISC</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -723,130 +723,10 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PO11132740</t>
+          <t>PO11255748</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VGASN1113QA3680</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00V11132025QA7028900</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>DD9293-100-10.5</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>PO11137372</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VGASN1113QA3680</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>00V11132025QA7666001</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>DD9293-100-8</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>6</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>PO11139762</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
@@ -863,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,17 +846,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1113QA3680</t>
+          <t>VGASN1125QA4410</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V11132025QA8179602</t>
+          <t>00V11252025QA8409300</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>900001103</t>
+          <t>900001221</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -984,38 +864,34 @@
           <t>3000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>CJ2242-100-L</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>78.2</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>26.8</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>31.563</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>85926.16</v>
+        <v>34641</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PO11133893</t>
+          <t>PO11255748</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2401098113</t>
+          <t>1903000001</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -1033,17 +909,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1113QA3680</t>
+          <t>VGASN1125QA4410</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V11132025QA4986703</t>
+          <t>00V11252025QA9579401</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>900001103</t>
+          <t>900001221</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1051,309 +927,37 @@
           <t>3000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>CJ2242-100-M</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>42.4</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>19.8</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>49.73</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>42395.76</v>
+        <v>34641</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>PO11138664</t>
+          <t>PO11255748</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2401098114</t>
+          <t>1903000001</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VGASN1113QA3680</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00V11132025QA9951904</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>900001103</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>DC4244-291-MISC</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>65</v>
-      </c>
-      <c r="K4" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>12.28</v>
-      </c>
-      <c r="M4" t="n">
-        <v>205563.15</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>PO11132929</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2401098115</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VGASN1113QA3680</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00V11132025QA3861905</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>900001103</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>DC4244-328-MISC</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>25.465</v>
-      </c>
-      <c r="M5" t="n">
-        <v>19448.572</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>PO11132740</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2401098116</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VGASN1113QA3680</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00V11132025QA7028900</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>900001103</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>DD9293-100-10.5</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>17</v>
-      </c>
-      <c r="L6" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>18482.4</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>PO11137372</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2401098111</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VGASN1113QA3680</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>00V11132025QA7666001</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>900001103</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>DD9293-100-8</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>63</v>
-      </c>
-      <c r="L7" t="n">
-        <v>30.372</v>
-      </c>
-      <c r="M7" t="n">
-        <v>190160.46</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>PO11139762</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2401098112</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1366,9 +970,443 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ENVN</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ASN_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>iLPN_ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ItemID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source_LPN</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Condition_Code_type</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Condition_Code_Desc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>UserId</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VGASN1125QA4410</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>00V11252025QA8409300</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MS - Multi-SKU</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VGASN1125QA4410</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00V11252025QA8409300</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MS - Multi-SKU</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN1125QA4410</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00V11252025QA9579401</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MS - Multi-SKU</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN1125QA4410</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00V11252025QA9579401</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MS - Multi-SKU</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGASN1125QA4410</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00V11252025QA9579401</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VGASN1125QA4410</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00V11252025QA9579401</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VGASN1125QA4410</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00V11252025QA8409300</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VGASN1125QA4410</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00V11252025QA8409300</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/J30/Output_files/iLPN_search_results.xlsx
+++ b/J30/Output_files/iLPN_search_results.xlsx
@@ -505,12 +505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1125QA4410</t>
+          <t>VGASN1126QA8010</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V11252025QA8409300</t>
+          <t>00V11262025QA3029500</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PO11255748</t>
+          <t>PO11266025</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1125QA4410</t>
+          <t>VGASN1126QA8010</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V11252025QA9579401</t>
+          <t>00V11262025QA2169401</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>PO11255748</t>
+          <t>PO11266025</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,12 +625,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VGASN1125QA4410</t>
+          <t>VGASN1126QA8010</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00V11252025QA8409300</t>
+          <t>00V11262025QA3029500</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>PO11255748</t>
+          <t>PO11266025</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VGASN1125QA4410</t>
+          <t>VGASN1126QA8010</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00V11252025QA9579401</t>
+          <t>00V11262025QA2169401</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PO11255748</t>
+          <t>PO11266025</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -846,17 +846,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1125QA4410</t>
+          <t>VGASN1126QA8010</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V11252025QA8409300</t>
+          <t>00V11262025QA2169401</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>900001221</t>
+          <t>900001224</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -864,34 +864,42 @@
           <t>3000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>420420-420-M</t>
+        </is>
+      </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>70.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>34.645</v>
       </c>
       <c r="M2" t="n">
-        <v>34641</v>
+        <v>41158.26</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PO11255748</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>PO11266025</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1903000001</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1903000001</t>
+          <t>2401000009</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -909,27 +917,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1125QA4410</t>
+          <t>VGASN1126QA8010</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V11252025QA9579401</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>900001221</t>
-        </is>
-      </c>
+          <t>T4000000000011262502</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>420420-420-M</t>
+        </is>
+      </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -944,20 +952,154 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>34641</v>
+        <v>81</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>PO11255748</t>
+          <t>PO11266025</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
+          <t>2402098049</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN1126QA8010</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00V11262025QA3029500</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>900001224</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31</v>
+      </c>
+      <c r="K4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L4" t="n">
+        <v>36.003</v>
+      </c>
+      <c r="M4" t="n">
+        <v>27825.6</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>PO11266025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>1903000001</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2401000007</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN1126QA8010</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>T4000000000011262503</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>34560</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>PO11266025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2402098048</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -970,443 +1112,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ENVN</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Plant</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ASN_ID</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>iLPN_ID</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ItemID</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Source_LPN</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Condition_Code_type</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Condition_Code_Desc</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>UserId</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>VGASN1125QA4410</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>00V11252025QA8409300</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>MS - Multi-SKU</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VGASN1125QA4410</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00V11252025QA8409300</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>MS - Multi-SKU</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VGASN1125QA4410</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00V11252025QA9579401</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>MS - Multi-SKU</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VGASN1125QA4410</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00V11252025QA9579401</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>MS - Multi-SKU</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VGASN1125QA4410</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00V11252025QA9579401</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>RL - Receiving lock</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VGASN1125QA4410</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>00V11252025QA9579401</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>RL - Receiving lock</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>VGASN1125QA4410</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>00V11252025QA8409300</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>RL - Receiving lock</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>VGASN1125QA4410</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>00V11252025QA8409300</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>RL - Receiving lock</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/J30/Output_files/iLPN_search_results.xlsx
+++ b/J30/Output_files/iLPN_search_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,12 +505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1126QA8010</t>
+          <t>VGASN1203QA1590</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V11262025QA3029500</t>
+          <t>00V12032025QA1811200</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MIXED_SKU</t>
+          <t>IN_VAS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>420420-420-M</t>
+          <t>927205-043-S</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -543,190 +543,10 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PO11266025</t>
+          <t>PO12033022</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VGASN1126QA8010</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00V11262025QA2169401</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>MIXED_SKU</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>420420-420-M</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>PO11266025</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VGASN1126QA8010</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00V11262025QA3029500</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>MIXED_SKU</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>PO11266025</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VGASN1126QA8010</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00V11262025QA2169401</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>MIXED_SKU</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>PO11266025</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
@@ -743,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -846,17 +666,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1126QA8010</t>
+          <t>VGASN1203QA1590</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V11262025QA2169401</t>
+          <t>00V12032025QA1811200</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>900001224</t>
+          <t>900001272</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -866,240 +686,35 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>420420-420-M</t>
+          <t>927205-043-S</t>
         </is>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>70.2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>34.645</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>41158.26</v>
+        <v>1200</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PO11266025</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1903000001</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2401000009</t>
-        </is>
-      </c>
+          <t>PO12033022</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VGASN1126QA8010</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>T4000000000011262502</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>420420-420-M</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>81</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>PO11266025</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2402098049</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VGASN1126QA8010</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00V11262025QA3029500</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>900001224</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>31</v>
-      </c>
-      <c r="K4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L4" t="n">
-        <v>36.003</v>
-      </c>
-      <c r="M4" t="n">
-        <v>27825.6</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>PO11266025</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1903000001</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2401000007</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VGASN1126QA8010</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>T4000000000011262503</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>34560</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>PO11266025</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2402098048</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1112,9 +727,128 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ENVN</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ASN_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>iLPN_ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ItemID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source_LPN</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Condition_Code_type</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Condition_Code_Desc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>UserId</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Barcode</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VGASN1203QA1590</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>00V12032025QA1811200</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>927205-043-S</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>00887232066765</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/J30/Output_files/iLPN_search_results.xlsx
+++ b/J30/Output_files/iLPN_search_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,12 +505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1203QA1590</t>
+          <t>0215055370</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V12032025QA1811200</t>
+          <t>20251204224646000001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IN_VAS</t>
+          <t>FIRST_SKU</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>927205-043-S</t>
+          <t>343880-202-12</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -543,10 +543,70 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PO12033022</t>
+          <t>3503910922</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0215055370</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>20251204224646000002</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>343880-202-12</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3503910922</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
@@ -563,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,17 +726,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1203QA1590</t>
+          <t>0215055370</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V12032025QA1811200</t>
+          <t>20251204224646000002</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>900001272</t>
+          <t>900001300</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -686,35 +746,114 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>927205-043-S</t>
+          <t>343880-202-12</t>
         </is>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>1200</v>
+        <v>81000</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PO12033022</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+          <t>3503910922</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1904000000</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2401098157</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0215055370</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>20251204224646000001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>900001300</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>343880-202-12</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J3" t="n">
+        <v>45</v>
+      </c>
+      <c r="K3" t="n">
+        <v>45</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>81000</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3503910922</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1904000000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2401098157</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -727,7 +866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,17 +944,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1203QA1590</t>
+          <t>0215055370</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V12032025QA1811200</t>
+          <t>20251204224646000001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>927205-043-S</t>
+          <t>343880-202-12</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -834,7 +973,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -844,7 +983,63 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00887232066765</t>
+          <t>00193154121674</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0215055370</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>20251204224646000002</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>343880-202-12</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>00193154121674</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/iLPN_search_results.xlsx
+++ b/J30/Output_files/iLPN_search_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,12 +505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0215055370</t>
+          <t>0215055325</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20251204224646000001</t>
+          <t>00009369430000189413</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FIRST_SKU</t>
+          <t>STORAGE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -530,11 +530,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>343880-202-12</t>
+          <t>487754-408-5</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3503910922</t>
+          <t>3503910931</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0215055370</t>
+          <t>0215055326</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20251204224646000002</t>
+          <t>00027112400000181326</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>STORAGE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -590,11 +590,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>343880-202-12</t>
+          <t>487754-408-4</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -603,10 +603,190 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3503910922</t>
+          <t>3503910932</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0215055444</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00033324160000421528</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3503910926</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0215055445</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00018335030000996223</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>3503910927</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0215055492</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00048562010000569466</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3503910925</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
@@ -623,7 +803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -726,19 +906,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0215055370</t>
+          <t>0215055325</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20251204224646000002</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>900001300</t>
-        </is>
-      </c>
+          <t>T4121020250000000005</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>3000</t>
@@ -746,7 +922,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>343880-202-12</t>
+          <t>487754-408-5</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -756,30 +932,26 @@
         <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>30.001</v>
       </c>
       <c r="M2" t="n">
-        <v>81000</v>
+        <v>800</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3503910922</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1904000000</t>
-        </is>
-      </c>
+          <t>3503910931</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2401098157</t>
+          <t>2402098054</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -797,63 +969,559 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0215055370</t>
+          <t>0215055325</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20251204224646000001</t>
+          <t>00009369430000189413</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>900001300</t>
+          <t>900001338</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40</v>
+      </c>
+      <c r="K3" t="n">
+        <v>40</v>
+      </c>
+      <c r="L3" t="n">
+        <v>30.001</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3503910931</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>3905000000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0215055326</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>T4121020250000000007</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>343880-202-12</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>487754-408-4</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>40</v>
-      </c>
-      <c r="J3" t="n">
-        <v>45</v>
-      </c>
-      <c r="K3" t="n">
-        <v>45</v>
-      </c>
-      <c r="L3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>81000</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>3503910922</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1904000000</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2401098157</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>40</v>
+      </c>
+      <c r="J4" t="n">
+        <v>40</v>
+      </c>
+      <c r="K4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L4" t="n">
+        <v>30.001</v>
+      </c>
+      <c r="M4" t="n">
+        <v>600</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3503910932</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2402098056</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0215055326</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00027112400000181326</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>900001338</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>40</v>
+      </c>
+      <c r="J5" t="n">
+        <v>40</v>
+      </c>
+      <c r="K5" t="n">
+        <v>40</v>
+      </c>
+      <c r="L5" t="n">
+        <v>30.001</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3503910932</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>3905000000</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0215055444</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>T4121020250000000006</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>40</v>
+      </c>
+      <c r="J6" t="n">
+        <v>40</v>
+      </c>
+      <c r="K6" t="n">
+        <v>40</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.001</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3503910926</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2402098055</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0215055444</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00033324160000421528</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>900001338</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>40</v>
+      </c>
+      <c r="J7" t="n">
+        <v>40</v>
+      </c>
+      <c r="K7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L7" t="n">
+        <v>30.001</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3503910926</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>3905000000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0215055445</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>T4121020250000000008</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>40</v>
+      </c>
+      <c r="J8" t="n">
+        <v>40</v>
+      </c>
+      <c r="K8" t="n">
+        <v>40</v>
+      </c>
+      <c r="L8" t="n">
+        <v>30.001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3503910927</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2402098053</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0215055445</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00018335030000996223</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>900001338</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>40</v>
+      </c>
+      <c r="J9" t="n">
+        <v>40</v>
+      </c>
+      <c r="K9" t="n">
+        <v>40</v>
+      </c>
+      <c r="L9" t="n">
+        <v>30.001</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3503910927</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>3905000000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0215055492</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>T4121020250000000004</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>40</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40</v>
+      </c>
+      <c r="K10" t="n">
+        <v>40</v>
+      </c>
+      <c r="L10" t="n">
+        <v>30.001</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3503910925</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2402098053</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0215055492</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00048562010000569466</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>900001338</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>40</v>
+      </c>
+      <c r="J11" t="n">
+        <v>40</v>
+      </c>
+      <c r="K11" t="n">
+        <v>40</v>
+      </c>
+      <c r="L11" t="n">
+        <v>30.001</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>3503910925</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3905000000</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -866,7 +1534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -944,22 +1612,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0215055370</t>
+          <t>0215055325</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20251204224646000001</t>
+          <t>T4121020250000000005</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>343880-202-12</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>487754-408-5</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>00009369430000189413</t>
+        </is>
+      </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -973,7 +1645,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +1655,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00193154121674</t>
+          <t>00197861516013</t>
         </is>
       </c>
     </row>
@@ -1000,22 +1672,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0215055370</t>
+          <t>0215055326</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20251204224646000002</t>
+          <t>T4121020250000000007</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>343880-202-12</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>487754-408-4</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>00027112400000181326</t>
+        </is>
+      </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1029,7 +1705,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1039,7 +1715,187 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00193154121674</t>
+          <t>00197861631600</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0215055444</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>T4121020250000000006</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>00033324160000421528</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>00194276397237</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0215055445</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>T4121020250000000008</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>00018335030000996223</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>00194276397220</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0215055492</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>T4121020250000000004</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>00048562010000569466</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>00194276397220</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/iLPN_search_results.xlsx
+++ b/J30/Output_files/iLPN_search_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,12 +505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0215055325</t>
+          <t>0215055509</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00009369430000189413</t>
+          <t>20251210221319000005</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -530,11 +530,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>487754-408-5</t>
+          <t>432997-128-13</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3503910931</t>
+          <t>3503912927</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0215055326</t>
+          <t>0215055509</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00027112400000181326</t>
+          <t>20251210221319000104</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,11 +590,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>487754-408-4</t>
+          <t>487754-408-5.5</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3503910932</t>
+          <t>3503912927</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,12 +625,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0215055444</t>
+          <t>0215055509</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00033324160000421528</t>
+          <t>20251210221319000119</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>432997-128-14</t>
+          <t>487754-408-5.5</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3503910926</t>
+          <t>3503912927</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0215055445</t>
+          <t>0215055509</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00018335030000996223</t>
+          <t>20251210221319000127</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -710,11 +710,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>432997-128-13</t>
+          <t>706510-100-L/XL</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3503910927</t>
+          <t>3503912928</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0215055492</t>
+          <t>0215055509</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00048562010000569466</t>
+          <t>20251210221319000131</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -770,11 +770,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>432997-128-13</t>
+          <t>706510-100-L/XL</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -783,10 +783,70 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3503910925</t>
+          <t>3503912928</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0215055509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20251210221319000139</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>706510-100-L/XL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3503912928</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
@@ -803,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,15 +966,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0215055325</t>
+          <t>0215055509</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>T4121020250000000005</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>20251210221319000005</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>900001378</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>3000</t>
@@ -922,7 +986,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>487754-408-5</t>
+          <t>432997-128-13</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -938,20 +1002,24 @@
         <v>40</v>
       </c>
       <c r="L2" t="n">
-        <v>30.001</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>800</v>
+        <v>64000</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3503910931</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>3503912927</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1904000000</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2402098054</t>
+          <t>2401098155</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -969,27 +1037,31 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0215055325</t>
+          <t>0215055509</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00009369430000189413</t>
+          <t>20251210221319000104</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>900001338</t>
+          <t>900001378</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>487754-408-5.5</t>
+        </is>
+      </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>40</v>
@@ -1001,22 +1073,26 @@
         <v>40</v>
       </c>
       <c r="L3" t="n">
-        <v>30.001</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>64000</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3503910931</t>
+          <t>3503912927</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>3905000000</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
+          <t>1904000000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2401098162</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1032,15 +1108,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0215055326</t>
+          <t>0215055509</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>T4121020250000000007</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>20251210221319000119</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>900001378</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>3000</t>
@@ -1048,7 +1128,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>487754-408-4</t>
+          <t>487754-408-5.5</t>
         </is>
       </c>
       <c r="H4" t="b">
@@ -1064,20 +1144,24 @@
         <v>40</v>
       </c>
       <c r="L4" t="n">
-        <v>30.001</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>600</v>
+        <v>64000</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3503910932</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>3503912927</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1904000000</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2402098056</t>
+          <t>2401098162</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -1095,27 +1179,31 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0215055326</t>
+          <t>0215055509</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00027112400000181326</t>
+          <t>20251210221319000127</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>900001338</t>
+          <t>900001378</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>706510-100-L/XL</t>
+        </is>
+      </c>
       <c r="H5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>40</v>
@@ -1127,22 +1215,26 @@
         <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>30.001</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>64000</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3503910932</t>
+          <t>3503912928</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>3905000000</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
+          <t>1904000000</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2401098159</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1158,15 +1250,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0215055444</t>
+          <t>0215055509</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>T4121020250000000006</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>20251210221319000131</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>900001378</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>3000</t>
@@ -1174,7 +1270,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>432997-128-14</t>
+          <t>706510-100-L/XL</t>
         </is>
       </c>
       <c r="H6" t="b">
@@ -1190,20 +1286,24 @@
         <v>40</v>
       </c>
       <c r="L6" t="n">
-        <v>30.001</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>1200</v>
+        <v>64000</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3503910926</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>3503912928</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1904000000</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2402098055</t>
+          <t>2401098159</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -1221,27 +1321,31 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0215055444</t>
+          <t>0215055509</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00033324160000421528</t>
+          <t>20251210221319000139</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>900001338</t>
+          <t>900001378</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>706510-100-L/XL</t>
+        </is>
+      </c>
       <c r="H7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>40</v>
@@ -1253,275 +1357,27 @@
         <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>30.001</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>64000</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3503910926</t>
+          <t>3503912928</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>3905000000</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
+          <t>1904000000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2401098159</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0215055445</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>T4121020250000000008</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>432997-128-13</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>40</v>
-      </c>
-      <c r="J8" t="n">
-        <v>40</v>
-      </c>
-      <c r="K8" t="n">
-        <v>40</v>
-      </c>
-      <c r="L8" t="n">
-        <v>30.001</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>3503910927</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2402098053</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0215055445</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>00018335030000996223</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>900001338</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>40</v>
-      </c>
-      <c r="J9" t="n">
-        <v>40</v>
-      </c>
-      <c r="K9" t="n">
-        <v>40</v>
-      </c>
-      <c r="L9" t="n">
-        <v>30.001</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>3503910927</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>3905000000</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0215055492</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>T4121020250000000004</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>432997-128-13</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>40</v>
-      </c>
-      <c r="J10" t="n">
-        <v>40</v>
-      </c>
-      <c r="K10" t="n">
-        <v>40</v>
-      </c>
-      <c r="L10" t="n">
-        <v>30.001</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1500</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>3503910925</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2402098053</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0215055492</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>00048562010000569466</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>900001338</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>40</v>
-      </c>
-      <c r="J11" t="n">
-        <v>40</v>
-      </c>
-      <c r="K11" t="n">
-        <v>40</v>
-      </c>
-      <c r="L11" t="n">
-        <v>30.001</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>3503910925</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>3905000000</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1534,372 +1390,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ENVN</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Plant</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ASN_ID</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>iLPN_ID</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ItemID</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Source_LPN</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Condition_Code_type</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Condition_Code_Desc</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>UserId</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Barcode</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0215055325</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>T4121020250000000005</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>487754-408-5</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>00009369430000189413</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>RL - Receiving lock</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>00197861516013</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0215055326</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>T4121020250000000007</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>487754-408-4</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>00027112400000181326</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>RL - Receiving lock</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>00197861631600</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0215055444</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>T4121020250000000006</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>432997-128-14</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>00033324160000421528</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>RL - Receiving lock</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>00194276397237</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0215055445</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>T4121020250000000008</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>432997-128-13</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>00018335030000996223</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>RL - Receiving lock</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>00194276397220</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0215055492</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>T4121020250000000004</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>432997-128-13</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>00048562010000569466</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>8</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>RL - Receiving lock</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>00194276397220</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/J30/Output_files/iLPN_search_results.xlsx
+++ b/J30/Output_files/iLPN_search_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,12 +505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0215055509</t>
+          <t>81ASN1219QA1341</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20251210221319000005</t>
+          <t>00081121920252811306</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>STORAGE</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -530,11 +530,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>432997-128-13</t>
+          <t>DH6619-010-1</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3503912927</t>
+          <t>PO12197234</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0215055509</t>
+          <t>81ASN1219QA1341</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20251210221319000104</t>
+          <t>00081121920251409307</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,11 +590,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>487754-408-5.5</t>
+          <t>DH6619-010-1</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3503912927</t>
+          <t>PO12197234</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,12 +625,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0215055509</t>
+          <t>81ASN1219QA1341</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20251210221319000119</t>
+          <t>00081121920256747004</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>STORAGE</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>487754-408-5.5</t>
+          <t>DH6619-010-4-5.5</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3503912927</t>
+          <t>PO12195146</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0215055509</t>
+          <t>81ASN1219QA1341</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20251210221319000127</t>
+          <t>00081121920258111805</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -710,11 +710,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>706510-100-L/XL</t>
+          <t>DH6619-010-4-5.5</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3503912928</t>
+          <t>PO12195146</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0215055509</t>
+          <t>81ASN1219QA2130</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20251210221319000131</t>
+          <t>00081121920251835402</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -770,11 +770,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>706510-100-L/XL</t>
+          <t>DH6619-010-1</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3503912928</t>
+          <t>PO12195181</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0215055509</t>
+          <t>81ASN1219QA2130</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20251210221319000139</t>
+          <t>00081121920253078403</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -830,11 +830,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>706510-100-L/XL</t>
+          <t>DH6619-010-1</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -843,10 +843,130 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3503912928</t>
+          <t>PO12195181</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>81ASN1219QA2130</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00081121920252220400</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>DH6619-010-4-5.5</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>PO12191837</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>81ASN1219QA2130</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00081121920251108701</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>DH6619-010-4-5.5</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>PO12191837</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
@@ -863,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,17 +1086,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0215055509</t>
+          <t>81ASN1219QA1341</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20251210221319000005</t>
+          <t>00081121920252811306</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>900001378</t>
+          <t>900001443</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -986,40 +1106,36 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>432997-128-13</t>
+          <t>DH6619-010-1</t>
         </is>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>64000</v>
+        <v>192</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3503912927</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1904000000</t>
-        </is>
-      </c>
+          <t>PO12197234</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2401098155</t>
+          <t>1008QAS000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -1037,17 +1153,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0215055509</t>
+          <t>81ASN1219QA1341</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20251210221319000104</t>
+          <t>00081121920251409307</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>900001378</t>
+          <t>900001443</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1057,40 +1173,36 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>487754-408-5.5</t>
+          <t>DH6619-010-1</t>
         </is>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>64000</v>
+        <v>192</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3503912927</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1904000000</t>
-        </is>
-      </c>
+          <t>PO12197234</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2401098162</t>
+          <t>1008MSS000</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -1108,17 +1220,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0215055509</t>
+          <t>81ASN1219QA1341</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20251210221319000119</t>
+          <t>00081121920256747004</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>900001378</t>
+          <t>900001443</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1128,40 +1240,36 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>487754-408-5.5</t>
+          <t>DH6619-010-4-5.5</t>
         </is>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>64000</v>
+        <v>432</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3503912927</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1904000000</t>
-        </is>
-      </c>
+          <t>PO12195146</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2401098162</t>
+          <t>1008QAS000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -1179,17 +1287,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0215055509</t>
+          <t>81ASN1219QA1341</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20251210221319000127</t>
+          <t>00081121920258111805</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>900001378</t>
+          <t>900001443</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1199,40 +1307,36 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>706510-100-L/XL</t>
+          <t>DH6619-010-4-5.5</t>
         </is>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>64000</v>
+        <v>432</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3503912928</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1904000000</t>
-        </is>
-      </c>
+          <t>PO12195146</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2401098159</t>
+          <t>1008MSS000</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -1250,17 +1354,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0215055509</t>
+          <t>81ASN1219QA2130</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20251210221319000131</t>
+          <t>00081121920251835402</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>900001378</t>
+          <t>900001443</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1270,40 +1374,36 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>706510-100-L/XL</t>
+          <t>DH6619-010-1</t>
         </is>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>64000</v>
+        <v>192</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3503912928</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1904000000</t>
-        </is>
-      </c>
+          <t>PO12195181</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2401098159</t>
+          <t>1008QAS000</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -1321,17 +1421,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0215055509</t>
+          <t>81ASN1219QA2130</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20251210221319000139</t>
+          <t>00081121920253078403</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>900001378</t>
+          <t>900001443</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1341,43 +1441,173 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>706510-100-L/XL</t>
+          <t>DH6619-010-1</t>
         </is>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>64000</v>
+        <v>192</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3503912928</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1904000000</t>
-        </is>
-      </c>
+          <t>PO12195181</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2401098159</t>
+          <t>1008MSS000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>81ASN1219QA2130</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00081121920252220400</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>900001443</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DH6619-010-4-5.5</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>432</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>PO12191837</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1008QAS000</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>81ASN1219QA2130</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00081121920251108701</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>900001443</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DH6619-010-4-5.5</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>432</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>PO12191837</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1008MSS000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1390,9 +1620,744 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ENVN</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ASN_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>iLPN_ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ItemID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source_LPN</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Condition_Code_type</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Condition_Code_Desc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>UserId</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Barcode</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>81ASN1219QA1341</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>00081121920251409307</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DH6619-010-1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>00196155790306</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>81ASN1219QA1341</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00081121920252811306</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DH6619-010-1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>QA - Quality Audit/Fail</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>00196155790306</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>81ASN1219QA1341</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00081121920252811306</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DH6619-010-1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>00196155790306</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>81ASN1219QA1341</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00081121920256747004</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DH6619-010-4-5.5</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>QA - Quality Audit/Fail</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>00196609177950</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>81ASN1219QA1341</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00081121920256747004</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DH6619-010-4-5.5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>00196609177950</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>81ASN1219QA1341</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00081121920258111805</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DH6619-010-4-5.5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>00196609177950</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>81ASN1219QA2130</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00081121920251108701</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DH6619-010-4-5.5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>00196609177950</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>81ASN1219QA2130</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00081121920251835402</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DH6619-010-1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>QA - Quality Audit/Fail</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>00196155790306</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>81ASN1219QA2130</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00081121920251835402</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DH6619-010-1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>00196155790306</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>81ASN1219QA2130</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00081121920252220400</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DH6619-010-4-5.5</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>QA - Quality Audit/Fail</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>00196609177950</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>81ASN1219QA2130</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00081121920252220400</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DH6619-010-4-5.5</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>00196609177950</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>81ASN1219QA2130</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00081121920253078403</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DH6619-010-1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>00196155790306</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/J30/Output_files/iLPN_search_results.xlsx
+++ b/J30/Output_files/iLPN_search_results.xlsx
@@ -505,12 +505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0215055575</t>
+          <t>81ASN0114QA1240</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20251224171909000001</t>
+          <t>00081011420265699200</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MIXED_SKU</t>
+          <t>STORAGE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -530,11 +530,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>343880-202-10</t>
+          <t>DD9293-100-11.5</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3503911028</t>
+          <t>PO01141685</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0215055575</t>
+          <t>81ASN0114QA1240</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20251224171909000001</t>
+          <t>00081011420269260301</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MIXED_SKU</t>
+          <t>STORAGE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -590,11 +590,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>343880-202-11</t>
+          <t>DD9293-100-11.5</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3503911028</t>
+          <t>PO01141685</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,12 +625,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0215055575</t>
+          <t>81ASN0114QA1240</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20251224171909000002</t>
+          <t>00081011420262662502</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MIXED_SKU</t>
+          <t>STORAGE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>343880-202-13</t>
+          <t>DD9293-100-11.5</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3503911028</t>
+          <t>PO01141685</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0215055575</t>
+          <t>81ASN0114QA1240</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20251224171909000002</t>
+          <t>00081011420267069203</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MIXED_SKU</t>
+          <t>STORAGE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -710,11 +710,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>343880-202-14</t>
+          <t>DD9293-100-11.5</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3503911028</t>
+          <t>PO01141685</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -846,12 +846,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0215055575</t>
+          <t>81ASN0114QA1240</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20251224171909000001</t>
+          <t>00081011420265699200</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -860,28 +860,32 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>DD9293-100-11.5</t>
+        </is>
+      </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>20.6</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>6138.594</v>
+        <v>62208</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3503911028</t>
+          <t>PO01141685</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -901,12 +905,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0215055575</t>
+          <t>81ASN0114QA1240</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20251224171909000002</t>
+          <t>00081011420269260301</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -915,33 +919,155 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>DD9293-100-11.5</t>
+        </is>
+      </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>20.6</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>6138.594</v>
+        <v>62208</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3503911028</t>
+          <t>PO01141685</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>81ASN0114QA1240</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00081011420262662502</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DD9293-100-11.5</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>62208</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>PO01141685</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>81ASN0114QA1240</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00081011420267069203</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DD9293-100-11.5</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>62208</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>PO01141685</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/iLPN_search_results.xlsx
+++ b/J30/Output_files/iLPN_search_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,17 +505,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0114QA1240</t>
+          <t>81ASN0122QA3510</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081011420265699200</t>
+          <t>00081012220265611400</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>899371-091-M</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PO01141685</t>
+          <t>PO01226817</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81ASN0114QA1240</t>
+          <t>81ASN0122QA3510</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00081011420269260301</t>
+          <t>00081012220261758801</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>899371-091-M</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -603,7 +603,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>PO01141685</t>
+          <t>PO01226817</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,17 +625,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>81ASN0114QA1240</t>
+          <t>81ASN0122QA3510</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00081011420262662502</t>
+          <t>00081012220261846502</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -645,12 +645,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>899371-091-M</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>PO01141685</t>
+          <t>PO01226817</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>81ASN0114QA1240</t>
+          <t>81ASN0122QA3510</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00081011420267069203</t>
+          <t>00081012220262826603</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>899371-091-M</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -723,10 +723,130 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PO01141685</t>
+          <t>PO01226817</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>81ASN0122QA3510</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00081012220267077804</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>899371-091-M</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>PO01226817</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>81ASN0122QA3510</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00081012220267664105</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>899371-091-M</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>PO01226817</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
@@ -743,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -846,50 +966,58 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0114QA1240</t>
+          <t>81ASN0122QA3510</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081011420265699200</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>00081012220267664105</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>900001514</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>899371-091-M</t>
         </is>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>62208</v>
+        <v>64000</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PO01141685</t>
+          <t>PO01226817</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2401098186</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -905,50 +1033,58 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81ASN0114QA1240</t>
+          <t>81ASN0122QA3510</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00081011420269260301</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>00081012220267077804</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>900001514</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>899371-091-M</t>
         </is>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>62208</v>
+        <v>64000</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>PO01141685</t>
+          <t>PO01226817</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2401098186</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -964,50 +1100,58 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>81ASN0114QA1240</t>
+          <t>81ASN0122QA3510</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00081011420262662502</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>00081012220262826603</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>900001514</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>899371-091-M</t>
         </is>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>62208</v>
+        <v>64000</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>PO01141685</t>
+          <t>PO01226817</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2401098186</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1023,51 +1167,193 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>81ASN0114QA1240</t>
+          <t>81ASN0122QA3510</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00081011420267069203</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>00081012220261846502</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>900001514</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>899371-091-M</t>
         </is>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>62208</v>
+        <v>64000</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>PO01141685</t>
+          <t>PO01226817</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2401098186</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>81ASN0122QA3510</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00081012220265611400</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>900001514</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>899371-091-M</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>40</v>
+      </c>
+      <c r="J6" t="n">
+        <v>40</v>
+      </c>
+      <c r="K6" t="n">
+        <v>40</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>PO01226817</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2401098186</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>81ASN0122QA3510</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00081012220261758801</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>900001514</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>899371-091-M</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>40</v>
+      </c>
+      <c r="J7" t="n">
+        <v>40</v>
+      </c>
+      <c r="K7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>PO01226817</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2401098186</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1080,9 +1366,408 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ENVN</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ASN_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>iLPN_ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ItemID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source_LPN</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Condition_Code_type</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Condition_Code_Desc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>UserId</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Barcode</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>81ASN0122QA3510</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>00081012220261758801</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>899371-091-M</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>00887229377935</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>81ASN0122QA3510</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00081012220261846502</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>899371-091-M</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>00887229377935</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>81ASN0122QA3510</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00081012220262826603</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>899371-091-M</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>00887229377935</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>81ASN0122QA3510</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00081012220265611400</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>899371-091-M</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>00887229377935</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>81ASN0122QA3510</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00081012220267077804</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>899371-091-M</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>00887229377935</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>81ASN0122QA3510</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00081012220267664105</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>899371-091-M</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>00887229377935</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/J30/Output_files/iLPN_search_results.xlsx
+++ b/J30/Output_files/iLPN_search_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,17 +505,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0122QA3510</t>
+          <t>0215055848</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081012220265611400</t>
+          <t>00015009940000834944</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>899371-091-M</t>
+          <t>415082-002-4Y</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PO01226817</t>
+          <t>3503914605</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81ASN0122QA3510</t>
+          <t>0215055848</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00081012220261758801</t>
+          <t>00015009940000834951</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>899371-091-M</t>
+          <t>415082-002-4Y</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -603,7 +603,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>PO01226817</t>
+          <t>3503914605</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,17 +625,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>81ASN0122QA3510</t>
+          <t>0215055848</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00081012220261846502</t>
+          <t>00015009940000834968</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -645,12 +645,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>899371-091-M</t>
+          <t>415082-002-4Y</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>PO01226817</t>
+          <t>3503914605</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>81ASN0122QA3510</t>
+          <t>0215055848</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00081012220262826603</t>
+          <t>00015009940000834975</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>899371-091-M</t>
+          <t>415082-002-4Y</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PO01226817</t>
+          <t>3503914605</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -745,17 +745,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>81ASN0122QA3510</t>
+          <t>0215055848</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00081012220267077804</t>
+          <t>00015009940000834982</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>899371-091-M</t>
+          <t>415082-002-4Y</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -783,7 +783,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>PO01226817</t>
+          <t>3503914605</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>81ASN0122QA3510</t>
+          <t>0215055848</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00081012220267664105</t>
+          <t>00015009940000834999</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -825,12 +825,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>899371-091-M</t>
+          <t>415082-002-4Y</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -843,10 +843,850 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>PO01226817</t>
+          <t>3503914605</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00015009940000835002</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00015009940000835019</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00015009940000835026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00015009940000835033</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00015009940000835040</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00015009940000835057</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00015009940000835064</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00015009940000835071</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00015009940000835088</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00015009940000835095</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00015009940000835101</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00015009940000835118</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00015009940000835125</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00015009940000835132</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>6</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
@@ -863,7 +1703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,58 +1806,50 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0122QA3510</t>
+          <t>0215055848</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081012220267664105</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>900001514</t>
-        </is>
-      </c>
+          <t>00015009940000834944</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>899371-091-M</t>
+          <t>415082-002-4Y</t>
         </is>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>40</v>
+        <v>12.9</v>
       </c>
       <c r="J2" t="n">
-        <v>40</v>
+        <v>20.6</v>
       </c>
       <c r="K2" t="n">
-        <v>40</v>
+        <v>23.1</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>64000</v>
+        <v>6138.594</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PO01226817</t>
+          <t>3503914605</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2401098186</t>
-        </is>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -1033,58 +1865,50 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81ASN0122QA3510</t>
+          <t>0215055848</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00081012220267077804</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>900001514</t>
-        </is>
-      </c>
+          <t>00015009940000834951</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>899371-091-M</t>
+          <t>415082-002-4Y</t>
         </is>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>40</v>
+        <v>12.9</v>
       </c>
       <c r="J3" t="n">
-        <v>40</v>
+        <v>20.6</v>
       </c>
       <c r="K3" t="n">
-        <v>40</v>
+        <v>23.1</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>64000</v>
+        <v>6138.594</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>PO01226817</t>
+          <t>3503914605</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2401098186</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1100,58 +1924,50 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>81ASN0122QA3510</t>
+          <t>0215055848</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00081012220262826603</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>900001514</t>
-        </is>
-      </c>
+          <t>00015009940000834968</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>899371-091-M</t>
+          <t>415082-002-4Y</t>
         </is>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>40</v>
+        <v>12.9</v>
       </c>
       <c r="J4" t="n">
-        <v>40</v>
+        <v>20.6</v>
       </c>
       <c r="K4" t="n">
-        <v>40</v>
+        <v>23.1</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>64000</v>
+        <v>6138.594</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>PO01226817</t>
+          <t>3503914605</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2401098186</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1167,58 +1983,50 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>81ASN0122QA3510</t>
+          <t>0215055848</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00081012220261846502</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>900001514</t>
-        </is>
-      </c>
+          <t>00015009940000834975</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>899371-091-M</t>
+          <t>415082-002-4Y</t>
         </is>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>40</v>
+        <v>12.9</v>
       </c>
       <c r="J5" t="n">
-        <v>40</v>
+        <v>20.6</v>
       </c>
       <c r="K5" t="n">
-        <v>40</v>
+        <v>23.1</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>64000</v>
+        <v>6138.594</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>PO01226817</t>
+          <t>3503914605</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2401098186</t>
-        </is>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1234,58 +2042,50 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>81ASN0122QA3510</t>
+          <t>0215055848</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00081012220265611400</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>900001514</t>
-        </is>
-      </c>
+          <t>00015009940000834982</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>899371-091-M</t>
+          <t>415082-002-4Y</t>
         </is>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>40</v>
+        <v>12.9</v>
       </c>
       <c r="J6" t="n">
-        <v>40</v>
+        <v>20.6</v>
       </c>
       <c r="K6" t="n">
-        <v>40</v>
+        <v>23.1</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>64000</v>
+        <v>6138.594</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>PO01226817</t>
+          <t>3503914605</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2401098186</t>
-        </is>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1301,59 +2101,877 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>81ASN0122QA3510</t>
+          <t>0215055848</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00081012220261758801</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>900001514</t>
-        </is>
-      </c>
+          <t>00015009940000834999</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>899371-091-M</t>
+          <t>415082-002-4Y</t>
         </is>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>40</v>
+        <v>12.9</v>
       </c>
       <c r="J7" t="n">
-        <v>40</v>
+        <v>20.6</v>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>23.1</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>64000</v>
+        <v>6138.594</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>PO01226817</t>
+          <t>3503914605</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2401098186</t>
-        </is>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00015009940000835002</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00015009940000835019</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00015009940000835026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00015009940000835033</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00015009940000835040</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00015009940000835057</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00015009940000835064</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00015009940000835071</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00015009940000835088</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00015009940000835095</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00015009940000835101</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00015009940000835118</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00015009940000835125</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0215055848</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00015009940000835132</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>3503914605</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1366,408 +2984,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ENVN</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Plant</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ASN_ID</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>iLPN_ID</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ItemID</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Source_LPN</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Condition_Code_type</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Condition_Code_Desc</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>UserId</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Barcode</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>81ASN0122QA3510</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>00081012220261758801</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>899371-091-M</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>RL - Receiving lock</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>00887229377935</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>81ASN0122QA3510</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00081012220261846502</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>899371-091-M</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>RL - Receiving lock</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>00887229377935</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>81ASN0122QA3510</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00081012220262826603</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>899371-091-M</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>RL - Receiving lock</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>00887229377935</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>81ASN0122QA3510</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00081012220265611400</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>899371-091-M</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>RL - Receiving lock</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>00887229377935</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>81ASN0122QA3510</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00081012220267077804</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>899371-091-M</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>RL - Receiving lock</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>00887229377935</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>81ASN0122QA3510</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>00081012220267664105</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>899371-091-M</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>RL - Receiving lock</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>00887229377935</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/J30/Output_files/iLPN_search_results.xlsx
+++ b/J30/Output_files/iLPN_search_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,12 +505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056175</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00015009940000834944</t>
+          <t>00069482730408451407</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -543,12 +543,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914655</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>nike-intg-user</t>
         </is>
       </c>
     </row>
@@ -565,12 +565,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056175</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00015009940000834951</t>
+          <t>00069482730408451414</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -603,12 +603,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914655</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>nike-intg-user</t>
         </is>
       </c>
     </row>
@@ -625,12 +625,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056175</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00015009940000834968</t>
+          <t>00069482730408451421</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -663,12 +663,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914655</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>nike-intg-user</t>
         </is>
       </c>
     </row>
@@ -685,12 +685,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056175</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00015009940000834975</t>
+          <t>00069482730408451438</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -723,12 +723,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914655</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>nike-intg-user</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056175</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00015009940000834982</t>
+          <t>00069482730408451445</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -783,12 +783,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914655</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>nike-intg-user</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056175</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00015009940000834999</t>
+          <t>00069482730408451452</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -843,12 +843,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914655</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>nike-intg-user</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056185</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00015009940000835002</t>
+          <t>00078192488401176941</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -903,7 +903,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914011</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056185</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00015009940000835019</t>
+          <t>00078192488401176958</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -963,7 +963,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914011</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056185</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00015009940000835026</t>
+          <t>00078192488401176965</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914011</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056185</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00015009940000835033</t>
+          <t>00078192488401176972</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914011</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056185</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00015009940000835040</t>
+          <t>00078192488401176989</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914011</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056185</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>00015009940000835057</t>
+          <t>00078192488401176996</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1203,490 +1203,10 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914011</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0215055848</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>00015009940000835064</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>3503914605</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0215055848</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>00015009940000835071</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>3503914605</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0215055848</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>00015009940000835088</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>3503914605</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0215055848</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>00015009940000835095</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>6</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>3503914605</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0215055848</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>00015009940000835101</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>6</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>3503914605</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0215055848</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>00015009940000835118</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>6</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>3503914605</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0215055848</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>00015009940000835125</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>6</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>3503914605</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0215055848</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>00015009940000835132</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>6</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>3503914605</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
@@ -1703,7 +1223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1806,12 +1326,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056175</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00015009940000834944</t>
+          <t>00069482730408451407</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -1822,7 +1342,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -1845,7 +1365,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914655</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -1865,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056175</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00015009940000834951</t>
+          <t>00069482730408451414</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -1881,7 +1401,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="H3" t="b">
@@ -1904,7 +1424,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914655</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -1924,12 +1444,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056175</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00015009940000834968</t>
+          <t>00069482730408451421</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -1940,7 +1460,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="H4" t="b">
@@ -1963,7 +1483,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914655</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -1983,12 +1503,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056175</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00015009940000834975</t>
+          <t>00069482730408451438</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1999,7 +1519,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -2022,7 +1542,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914655</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -2042,12 +1562,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056175</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00015009940000834982</t>
+          <t>00069482730408451445</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -2058,7 +1578,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="H6" t="b">
@@ -2081,7 +1601,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914655</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -2101,12 +1621,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056175</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00015009940000834999</t>
+          <t>00069482730408451452</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -2117,7 +1637,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="H7" t="b">
@@ -2140,7 +1660,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914655</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -2160,12 +1680,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056185</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00015009940000835002</t>
+          <t>00078192488401176941</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -2176,7 +1696,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="H8" t="b">
@@ -2199,7 +1719,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914011</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -2219,12 +1739,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056185</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00015009940000835019</t>
+          <t>00078192488401176958</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -2235,7 +1755,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="H9" t="b">
@@ -2258,7 +1778,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914011</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -2278,12 +1798,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056185</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00015009940000835026</t>
+          <t>00078192488401176965</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -2294,7 +1814,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="H10" t="b">
@@ -2317,7 +1837,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914011</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -2337,12 +1857,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056185</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00015009940000835033</t>
+          <t>00078192488401176972</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -2353,7 +1873,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -2376,7 +1896,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914011</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -2396,12 +1916,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056185</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00015009940000835040</t>
+          <t>00078192488401176989</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -2412,7 +1932,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="H12" t="b">
@@ -2435,7 +1955,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914011</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -2455,12 +1975,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0215055848</t>
+          <t>0215056185</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>00015009940000835057</t>
+          <t>00078192488401176996</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -2471,7 +1991,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>415082-002-4Y</t>
+          <t>AJ7566-085-S</t>
         </is>
       </c>
       <c r="H13" t="b">
@@ -2494,484 +2014,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3503914605</t>
+          <t>3503914011</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0215055848</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>00015009940000835064</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>6138.594</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>3503914605</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0215055848</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>00015009940000835071</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>6138.594</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>3503914605</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0215055848</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>00015009940000835088</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6138.594</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>3503914605</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0215055848</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>00015009940000835095</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="K17" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>6138.594</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>3503914605</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0215055848</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>00015009940000835101</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="K18" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>6138.594</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>3503914605</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0215055848</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>00015009940000835118</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>6138.594</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>3503914605</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0215055848</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>00015009940000835125</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6138.594</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>3503914605</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0215055848</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>00015009940000835132</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J21" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="K21" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>6138.594</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>3503914605</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/iLPN_search_results.xlsx
+++ b/J30/Output_files/iLPN_search_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,17 +505,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0215056175</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00069482730408451407</t>
+          <t>00024985677904232493</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3503914655</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>nike-intg-user</t>
+          <t>vgana3</t>
         </is>
       </c>
     </row>
@@ -565,17 +565,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0215056175</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00069482730408451414</t>
+          <t>00024985677904232509</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3503914655</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>nike-intg-user</t>
+          <t>vgana3</t>
         </is>
       </c>
     </row>
@@ -625,17 +625,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0215056175</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00069482730408451421</t>
+          <t>00024985677904232516</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3503914655</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>nike-intg-user</t>
+          <t>vgana3</t>
         </is>
       </c>
     </row>
@@ -685,17 +685,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0215056175</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00069482730408451438</t>
+          <t>00024985677904232523</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3503914655</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>nike-intg-user</t>
+          <t>vgana3</t>
         </is>
       </c>
     </row>
@@ -745,17 +745,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0215056175</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00069482730408451445</t>
+          <t>00024985677904232530</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3503914655</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>nike-intg-user</t>
+          <t>vgana3</t>
         </is>
       </c>
     </row>
@@ -805,17 +805,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0215056175</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00069482730408451452</t>
+          <t>00024985677904232547</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3503914655</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>nike-intg-user</t>
+          <t>vgana3</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0215056185</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00078192488401176941</t>
+          <t>00024985677904232554</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3503914011</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -925,17 +925,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0215056185</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00078192488401176958</t>
+          <t>00024985677904232561</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>3503914011</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0215056185</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00078192488401176965</t>
+          <t>00024985677904232578</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3503914011</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0215056185</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00078192488401176972</t>
+          <t>00024985677904232585</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1083,130 +1083,10 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3503914011</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0215056185</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>00078192488401176989</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>AJ7566-085-S</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>3503914011</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0215056185</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>00078192488401176996</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>AJ7566-085-S</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>3503914011</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
@@ -1223,7 +1103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1326,18 +1206,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0215056175</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00069482730408451407</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>00024985677904232493</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>900001666</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1365,11 +1249,15 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3503914655</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1902000000</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -1385,18 +1273,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0215056175</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00069482730408451414</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>00024985677904232509</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>900001666</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1408,27 +1300,31 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>12.9</v>
+        <v>40</v>
       </c>
       <c r="J3" t="n">
-        <v>20.6</v>
+        <v>40</v>
       </c>
       <c r="K3" t="n">
-        <v>23.1</v>
+        <v>40</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>6138.594</v>
+        <v>64000</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3503914655</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2401098225</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1444,18 +1340,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0215056175</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00069482730408451421</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>00024985677904232516</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>900001666</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1467,27 +1367,31 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>12.9</v>
+        <v>40</v>
       </c>
       <c r="J4" t="n">
-        <v>20.6</v>
+        <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>23.1</v>
+        <v>40</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>6138.594</v>
+        <v>64000</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3503914655</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2401098225</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1503,18 +1407,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0215056175</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00069482730408451438</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>00024985677904232523</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>900001666</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1526,27 +1434,31 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>12.9</v>
+        <v>40</v>
       </c>
       <c r="J5" t="n">
-        <v>20.6</v>
+        <v>40</v>
       </c>
       <c r="K5" t="n">
-        <v>23.1</v>
+        <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>6138.594</v>
+        <v>64000</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3503914655</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2401098225</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1562,18 +1474,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0215056175</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00069482730408451445</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>00024985677904232530</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>900001666</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1585,27 +1501,31 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>12.9</v>
+        <v>40</v>
       </c>
       <c r="J6" t="n">
-        <v>20.6</v>
+        <v>40</v>
       </c>
       <c r="K6" t="n">
-        <v>23.1</v>
+        <v>40</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>6138.594</v>
+        <v>64000</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3503914655</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2401098225</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1621,18 +1541,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0215056175</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00069482730408451452</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>00024985677904232547</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>900001666</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1644,27 +1568,31 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>12.9</v>
+        <v>40</v>
       </c>
       <c r="J7" t="n">
-        <v>20.6</v>
+        <v>40</v>
       </c>
       <c r="K7" t="n">
-        <v>23.1</v>
+        <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>6138.594</v>
+        <v>64000</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3503914655</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2401098225</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1680,18 +1608,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0215056185</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00078192488401176941</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>00024985677904232554</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>900001666</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1703,27 +1635,31 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>12.9</v>
+        <v>40</v>
       </c>
       <c r="J8" t="n">
-        <v>20.6</v>
+        <v>40</v>
       </c>
       <c r="K8" t="n">
-        <v>23.1</v>
+        <v>40</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
-        <v>6138.594</v>
+        <v>64000</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3503914011</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2401098225</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1739,18 +1675,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0215056185</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00078192488401176958</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>00024985677904232561</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>900001666</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1762,27 +1702,31 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>12.9</v>
+        <v>40</v>
       </c>
       <c r="J9" t="n">
-        <v>20.6</v>
+        <v>40</v>
       </c>
       <c r="K9" t="n">
-        <v>23.1</v>
+        <v>40</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>6138.594</v>
+        <v>64000</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3503914011</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2401098225</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1798,18 +1742,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0215056185</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00078192488401176965</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>00024985677904232578</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>900001666</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1821,27 +1769,31 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>12.9</v>
+        <v>40</v>
       </c>
       <c r="J10" t="n">
-        <v>20.6</v>
+        <v>40</v>
       </c>
       <c r="K10" t="n">
-        <v>23.1</v>
+        <v>40</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>6138.594</v>
+        <v>64000</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3503914011</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2401098225</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1857,18 +1809,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0215056185</t>
+          <t>0215056059</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00078192488401176972</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>00024985677904232585</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>900001666</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1880,146 +1836,32 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>12.9</v>
+        <v>40</v>
       </c>
       <c r="J11" t="n">
-        <v>20.6</v>
+        <v>40</v>
       </c>
       <c r="K11" t="n">
-        <v>23.1</v>
+        <v>40</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>6138.594</v>
+        <v>64000</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3503914011</t>
+          <t>3503913940</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2401098225</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0215056185</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>00078192488401176989</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>AJ7566-085-S</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>6138.594</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>3503914011</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0215056185</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>00078192488401176996</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>AJ7566-085-S</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="K13" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>6138.594</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>3503914011</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2032,9 +1874,632 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ENVN</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ASN_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>iLPN_ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ItemID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source_LPN</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Condition_Code_type</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Condition_Code_Desc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>UserId</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Barcode</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0215056059</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>00024985677904232493</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>00196153941106</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0215056059</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00024985677904232509</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>00196153941106</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0215056059</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00024985677904232516</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>00196153941106</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0215056059</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00024985677904232523</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>00196153941106</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0215056059</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00024985677904232530</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>00196153941106</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0215056059</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00024985677904232547</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>00196153941106</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0215056059</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00024985677904232554</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>00196153941106</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0215056059</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00024985677904232561</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>00196153941106</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0215056059</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00024985677904232578</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>00196153941106</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0215056059</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00024985677904232585</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>00196153941106</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/J30/Output_files/iLPN_search_results.xlsx
+++ b/J30/Output_files/iLPN_search_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,12 +505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00024985677904232493</t>
+          <t>20260318210346000001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ0599-010-3XL</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3503913940</t>
+          <t>3503914562</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00024985677904232509</t>
+          <t>20260318210346000002</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ0599-010-3XL</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -603,7 +603,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3503913940</t>
+          <t>3503914562</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,12 +625,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00024985677904232516</t>
+          <t>20260318210346000003</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ0599-010-L</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3503913940</t>
+          <t>3503914562</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00024985677904232523</t>
+          <t>20260318210346000004</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ0599-010-L</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3503913940</t>
+          <t>3503914562</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -745,17 +745,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00024985677904232530</t>
+          <t>20260318210346000021</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ2624-451-L</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -783,7 +783,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3503913940</t>
+          <t>3503914562</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00024985677904232547</t>
+          <t>20260318210346000022</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -825,12 +825,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ2624-451-L</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -843,7 +843,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3503913940</t>
+          <t>3503914562</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00024985677904232554</t>
+          <t>20260318210346000023</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ2624-451-XL</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -903,7 +903,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3503913940</t>
+          <t>3503914562</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -925,17 +925,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00024985677904232561</t>
+          <t>20260318210346000024</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ2624-451-XL</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -963,7 +963,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>3503913940</t>
+          <t>3503914562</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00024985677904232578</t>
+          <t>20260318210346000025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HQ0027-010-3XL</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3503913940</t>
+          <t>3503914562</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00024985677904232585</t>
+          <t>20260318210346000026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HQ0027-010-3XL</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1083,10 +1083,610 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3503913940</t>
+          <t>3503914562</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20260318210346000027</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>HQ0027-010-L</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20260318210346000028</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>HQ0027-010-L</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>20260318210346000029</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>HQ0027-100-5XL</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20260318210346000030</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>HQ0027-100-5XL</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20260318210346000031</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>HQ0027-100-M</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>20260318210346000032</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>HQ0027-100-M</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20260318210346000033</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>HQ0027-744-4XL</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>20260318210346000034</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>HQ0027-744-4XL</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>20260318210346000035</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>HQ0027-744-M</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>20260318210346000036</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>HQ0027-744-M</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>6</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
@@ -1103,7 +1703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1206,17 +1806,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00024985677904232493</t>
+          <t>20260318210346000001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>900001666</t>
+          <t>900001730</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1226,36 +1826,40 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ0599-010-3XL</t>
         </is>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>12.9</v>
+        <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>20.6</v>
+        <v>40</v>
       </c>
       <c r="K2" t="n">
-        <v>23.1</v>
+        <v>40</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>6138.594</v>
+        <v>64000</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3503913940</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>3912000000</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1902000000</t>
+          <t>1008MSS000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -1273,17 +1877,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00024985677904232509</t>
+          <t>20260318210346000002</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>900001666</t>
+          <t>900001730</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1293,7 +1897,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ0599-010-3XL</t>
         </is>
       </c>
       <c r="H3" t="b">
@@ -1316,13 +1920,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3503913940</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>3912000000</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2401098225</t>
+          <t>1008MSS000</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -1340,17 +1948,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00024985677904232516</t>
+          <t>20260318210346000003</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>900001666</t>
+          <t>900001730</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1360,7 +1968,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ0599-010-L</t>
         </is>
       </c>
       <c r="H4" t="b">
@@ -1383,13 +1991,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3503913940</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>3912000000</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2401098225</t>
+          <t>1008MSS000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -1407,17 +2019,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00024985677904232523</t>
+          <t>20260318210346000004</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>900001666</t>
+          <t>900001730</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1427,7 +2039,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ0599-010-L</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -1450,13 +2062,17 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3503913940</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>3912000000</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2401098225</t>
+          <t>1008MSS000</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -1474,58 +2090,50 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00024985677904232530</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>900001666</t>
-        </is>
-      </c>
+          <t>20260318210346000021</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ2624-451-L</t>
         </is>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>40</v>
+        <v>12.9</v>
       </c>
       <c r="J6" t="n">
-        <v>40</v>
+        <v>20.6</v>
       </c>
       <c r="K6" t="n">
-        <v>40</v>
+        <v>23.1</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>64000</v>
+        <v>6138.594</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3503913940</t>
+          <t>3503914562</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2401098225</t>
-        </is>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1541,58 +2149,50 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00024985677904232547</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>900001666</t>
-        </is>
-      </c>
+          <t>20260318210346000022</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ2624-451-L</t>
         </is>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>40</v>
+        <v>12.9</v>
       </c>
       <c r="J7" t="n">
-        <v>40</v>
+        <v>20.6</v>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>23.1</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>64000</v>
+        <v>6138.594</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3503913940</t>
+          <t>3503914562</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2401098225</t>
-        </is>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1608,58 +2208,50 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00024985677904232554</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>900001666</t>
-        </is>
-      </c>
+          <t>20260318210346000023</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ2624-451-XL</t>
         </is>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>40</v>
+        <v>12.9</v>
       </c>
       <c r="J8" t="n">
-        <v>40</v>
+        <v>20.6</v>
       </c>
       <c r="K8" t="n">
-        <v>40</v>
+        <v>23.1</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>64000</v>
+        <v>6138.594</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3503913940</t>
+          <t>3503914562</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2401098225</t>
-        </is>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1675,58 +2267,50 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00024985677904232561</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>900001666</t>
-        </is>
-      </c>
+          <t>20260318210346000024</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ2624-451-XL</t>
         </is>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>40</v>
+        <v>12.9</v>
       </c>
       <c r="J9" t="n">
-        <v>40</v>
+        <v>20.6</v>
       </c>
       <c r="K9" t="n">
-        <v>40</v>
+        <v>23.1</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>64000</v>
+        <v>6138.594</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3503913940</t>
+          <t>3503914562</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2401098225</t>
-        </is>
-      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1742,58 +2326,50 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00024985677904232578</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>900001666</t>
-        </is>
-      </c>
+          <t>20260318210346000025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HQ0027-010-3XL</t>
         </is>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>40</v>
+        <v>12.9</v>
       </c>
       <c r="J10" t="n">
-        <v>40</v>
+        <v>20.6</v>
       </c>
       <c r="K10" t="n">
-        <v>40</v>
+        <v>23.1</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>64000</v>
+        <v>6138.594</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3503913940</t>
+          <t>3503914562</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2401098225</t>
-        </is>
-      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1809,59 +2385,641 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00024985677904232585</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>900001666</t>
-        </is>
-      </c>
+          <t>20260318210346000026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HQ0027-010-3XL</t>
         </is>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>40</v>
+        <v>12.9</v>
       </c>
       <c r="J11" t="n">
-        <v>40</v>
+        <v>20.6</v>
       </c>
       <c r="K11" t="n">
-        <v>40</v>
+        <v>23.1</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>64000</v>
+        <v>6138.594</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3503913940</t>
+          <t>3503914562</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2401098225</t>
-        </is>
-      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20260318210346000027</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HQ0027-010-L</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20260318210346000028</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HQ0027-010-L</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>20260318210346000029</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HQ0027-100-5XL</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20260318210346000030</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HQ0027-100-5XL</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20260318210346000031</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HQ0027-100-M</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>20260318210346000032</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HQ0027-100-M</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20260318210346000033</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HQ0027-744-4XL</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>20260318210346000034</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HQ0027-744-4XL</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>20260318210346000035</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>HQ0027-744-M</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>20260318210346000036</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HQ0027-744-M</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>6138.594</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>3503914562</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1874,7 +3032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1952,17 +3110,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00024985677904232493</t>
+          <t>20260318210346000001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ0599-010-3XL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -1991,7 +3149,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00196153941106</t>
+          <t>00197859538317</t>
         </is>
       </c>
     </row>
@@ -2008,17 +3166,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00024985677904232509</t>
+          <t>20260318210346000002</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ0599-010-3XL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2047,7 +3205,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00196153941106</t>
+          <t>00197859538317</t>
         </is>
       </c>
     </row>
@@ -2064,17 +3222,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00024985677904232516</t>
+          <t>20260318210346000003</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ0599-010-L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2103,7 +3261,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>00196153941106</t>
+          <t>00197859543502</t>
         </is>
       </c>
     </row>
@@ -2120,17 +3278,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00024985677904232523</t>
+          <t>20260318210346000004</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ0599-010-L</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -2159,7 +3317,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>00196153941106</t>
+          <t>00197859543502</t>
         </is>
       </c>
     </row>
@@ -2176,17 +3334,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00024985677904232530</t>
+          <t>20260318210346000005</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ0958-233-3XL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -2215,7 +3373,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>00196153941106</t>
+          <t>00197860171985</t>
         </is>
       </c>
     </row>
@@ -2232,17 +3390,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00024985677904232547</t>
+          <t>20260318210346000006</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ0958-233-3XL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -2271,7 +3429,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>00196153941106</t>
+          <t>00197860171985</t>
         </is>
       </c>
     </row>
@@ -2288,17 +3446,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00024985677904232554</t>
+          <t>20260318210346000007</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ0958-233-4XL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -2327,7 +3485,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>00196153941106</t>
+          <t>00197860171428</t>
         </is>
       </c>
     </row>
@@ -2344,17 +3502,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00024985677904232561</t>
+          <t>20260318210346000008</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ0958-233-4XL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -2383,7 +3541,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>00196153941106</t>
+          <t>00197860171428</t>
         </is>
       </c>
     </row>
@@ -2400,17 +3558,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00024985677904232578</t>
+          <t>20260318210346000009</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ2160-234-4XL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -2439,7 +3597,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>00196153941106</t>
+          <t>00197861286169</t>
         </is>
       </c>
     </row>
@@ -2456,17 +3614,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0215056059</t>
+          <t>0215056616</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00024985677904232585</t>
+          <t>20260318210346000010</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AJ7566-085-S</t>
+          <t>HJ2160-234-4XL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -2495,7 +3653,567 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>00196153941106</t>
+          <t>00197861286169</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20260318210346000011</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HJ2160-234-S</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>00197859181988</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20260318210346000012</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HJ2160-234-S</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>00197859181988</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>20260318210346000013</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>HJ2219-100-3XL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>00197861367400</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20260318210346000014</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>HJ2219-100-3XL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>00197861367400</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20260318210346000015</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HJ2219-100-S</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>00197859692194</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>20260318210346000016</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HJ2219-100-S</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>00197859692194</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20260318210346000017</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HJ2534-010-L</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>00197859923588</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>20260318210346000018</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>HJ2534-010-L</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>00197859923588</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>20260318210346000019</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>HJ2534-010-M</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>00197859935888</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0215056616</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>20260318210346000020</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>HJ2534-010-M</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>00197859935888</t>
         </is>
       </c>
     </row>
